--- a/playlists_04_B.xlsx
+++ b/playlists_04_B.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1199" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="58">
   <si>
     <t>bob sinclar</t>
   </si>
@@ -34,124 +34,127 @@
     <t>academia</t>
   </si>
   <si>
+    <t>boris</t>
+  </si>
+  <si>
+    <t>24abT5NjGCIyuT0ivqYoBl</t>
+  </si>
+  <si>
+    <t>fatsync</t>
+  </si>
+  <si>
+    <t>6H11mqvcME7dP66oQ9Nf8U</t>
+  </si>
+  <si>
+    <t>aca</t>
+  </si>
+  <si>
+    <t>calvin harris</t>
+  </si>
+  <si>
+    <t>7CajNmpbOovFoOoasH2HaY</t>
+  </si>
+  <si>
+    <t>acade</t>
+  </si>
+  <si>
+    <t>alok</t>
+  </si>
+  <si>
+    <t>0NGAZxHanS9e0iNHpR8f2W</t>
+  </si>
+  <si>
+    <t>eletro</t>
+  </si>
+  <si>
+    <t>33uRcSdNVZijCXq6qQnpuU</t>
+  </si>
+  <si>
+    <t>victor lou</t>
+  </si>
+  <si>
+    <t>063wYkWkHrq5L5YWdrqjEt</t>
+  </si>
+  <si>
+    <t>academ</t>
+  </si>
+  <si>
+    <t>miss monique</t>
+  </si>
+  <si>
+    <t>29TpNOsTNYbLb6Xa10H0PR</t>
+  </si>
+  <si>
+    <t>dance</t>
+  </si>
+  <si>
+    <t>4gHf3sODPo6qXPGnsuPU26</t>
+  </si>
+  <si>
+    <t>electro</t>
+  </si>
+  <si>
+    <t>6HqTlMOvZPVSGaRrCFkBLV</t>
+  </si>
+  <si>
+    <t>fezzo</t>
+  </si>
+  <si>
+    <t>2tEWqiatl7q8hW7xyMwrtB</t>
+  </si>
+  <si>
+    <t>bor</t>
+  </si>
+  <si>
+    <t>anyma</t>
+  </si>
+  <si>
+    <t>4iBwchw0U0GZv5RfVYSMxN</t>
+  </si>
+  <si>
+    <t>vintage culture</t>
+  </si>
+  <si>
+    <t>28uJnu5EsrGml2tBd7y8ts</t>
+  </si>
+  <si>
+    <t>tiesto</t>
+  </si>
+  <si>
+    <t>2o5jDhtHVPhrJdv3cEQ99Z</t>
+  </si>
+  <si>
+    <t>vintage</t>
+  </si>
+  <si>
+    <t>7xuujsdt7kn1e9gKjttt4g</t>
+  </si>
+  <si>
+    <t>claptone</t>
+  </si>
+  <si>
+    <t>4mncDFjVLUa3s025Tct3Ry</t>
+  </si>
+  <si>
+    <t>28vvQFdeLvoSwwjQLyydyu</t>
+  </si>
+  <si>
+    <t>eletronico</t>
+  </si>
+  <si>
+    <t>martin garrix</t>
+  </si>
+  <si>
+    <t>60d24wfXkVzDSfLS6hyCjZ</t>
+  </si>
+  <si>
+    <t>2iiczh5fqfyDOq2rI90Rgk</t>
+  </si>
+  <si>
+    <t>5mcxg1rIaDA7hjzydZNSVk</t>
+  </si>
+  <si>
     <t>electro house</t>
-  </si>
-  <si>
-    <t>6HqTlMOvZPVSGaRrCFkBLV</t>
-  </si>
-  <si>
-    <t>fatsync</t>
-  </si>
-  <si>
-    <t>6H11mqvcME7dP66oQ9Nf8U</t>
-  </si>
-  <si>
-    <t>aca</t>
-  </si>
-  <si>
-    <t>calvin harris</t>
-  </si>
-  <si>
-    <t>7CajNmpbOovFoOoasH2HaY</t>
-  </si>
-  <si>
-    <t>acade</t>
-  </si>
-  <si>
-    <t>alok</t>
-  </si>
-  <si>
-    <t>0NGAZxHanS9e0iNHpR8f2W</t>
-  </si>
-  <si>
-    <t>33uRcSdNVZijCXq6qQnpuU</t>
-  </si>
-  <si>
-    <t>victor lou</t>
-  </si>
-  <si>
-    <t>063wYkWkHrq5L5YWdrqjEt</t>
-  </si>
-  <si>
-    <t>academ</t>
-  </si>
-  <si>
-    <t>miss monique</t>
-  </si>
-  <si>
-    <t>29TpNOsTNYbLb6Xa10H0PR</t>
-  </si>
-  <si>
-    <t>dance 2026 as melhores</t>
-  </si>
-  <si>
-    <t>4gHf3sODPo6qXPGnsuPU26</t>
-  </si>
-  <si>
-    <t>electro house 2026</t>
-  </si>
-  <si>
-    <t>boris brejcha</t>
-  </si>
-  <si>
-    <t>6caPJFLv1wesmM7gwK1ACy</t>
-  </si>
-  <si>
-    <t>boris brejcha 2026</t>
-  </si>
-  <si>
-    <t>24abT5NjGCIyuT0ivqYoBl</t>
-  </si>
-  <si>
-    <t>anyma</t>
-  </si>
-  <si>
-    <t>4iBwchw0U0GZv5RfVYSMxN</t>
-  </si>
-  <si>
-    <t>vintage culture</t>
-  </si>
-  <si>
-    <t>28uJnu5EsrGml2tBd7y8ts</t>
-  </si>
-  <si>
-    <t>eletronico</t>
-  </si>
-  <si>
-    <t>tiesto</t>
-  </si>
-  <si>
-    <t>2o5jDhtHVPhrJdv3cEQ99Z</t>
-  </si>
-  <si>
-    <t>vintage</t>
-  </si>
-  <si>
-    <t>7xuujsdt7kn1e9gKjttt4g</t>
-  </si>
-  <si>
-    <t>claptone</t>
-  </si>
-  <si>
-    <t>4mncDFjVLUa3s025Tct3Ry</t>
-  </si>
-  <si>
-    <t>28vvQFdeLvoSwwjQLyydyu</t>
-  </si>
-  <si>
-    <t>boris</t>
-  </si>
-  <si>
-    <t>martin garrix</t>
-  </si>
-  <si>
-    <t>60d24wfXkVzDSfLS6hyCjZ</t>
-  </si>
-  <si>
-    <t>2iiczh5fqfyDOq2rI90Rgk</t>
-  </si>
-  <si>
-    <t>5mcxg1rIaDA7hjzydZNSVk</t>
   </si>
   <si>
     <t>garrix</t>
@@ -258,8 +261,8 @@
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
@@ -267,8 +270,8 @@
     <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -588,22 +591,24 @@
       <c r="E6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F6" s="1"/>
+      <c r="F6" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="G6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H6" s="1"/>
     </row>
     <row r="7" ht="36.0" customHeight="1">
       <c r="C7" s="1"/>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>3</v>
@@ -615,16 +620,16 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="D8" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="F8" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="G8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="9" ht="36.0" customHeight="1">
@@ -632,10 +637,10 @@
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>11</v>
@@ -647,33 +652,33 @@
     <row r="10" ht="36.0" customHeight="1">
       <c r="C10" s="1"/>
       <c r="D10" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" ht="36.0" customHeight="1">
       <c r="A11" s="3"/>
       <c r="B11" s="4"/>
       <c r="C11" s="1"/>
-      <c r="D11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="1" t="s">
+      <c r="D11" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G11" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H11" s="1"/>
     </row>
@@ -699,10 +704,10 @@
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>6</v>
@@ -714,16 +719,16 @@
     <row r="14" ht="36.0" customHeight="1">
       <c r="C14" s="1"/>
       <c r="D14" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="F14" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="G14" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H14" s="1"/>
     </row>
@@ -749,16 +754,16 @@
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>23</v>
+        <v>32</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" ht="36.0" customHeight="1">
@@ -769,7 +774,7 @@
         <v>37</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>2</v>
@@ -788,22 +793,22 @@
       <c r="E18" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>7</v>
+      <c r="F18" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" ht="36.0" customHeight="1">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>27</v>
+      <c r="D19" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>6</v>
@@ -813,7 +818,7 @@
       </c>
     </row>
     <row r="20" ht="36.0" customHeight="1">
-      <c r="A20" s="8"/>
+      <c r="A20" s="5"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1" t="s">
@@ -833,10 +838,10 @@
       <c r="A21" s="3"/>
       <c r="B21" s="4"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="8" t="s">
         <v>40</v>
       </c>
       <c r="F21" s="2" t="s">
@@ -850,17 +855,17 @@
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
-      <c r="D22" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="1" t="s">
+      <c r="D22" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E22" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G22" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H22" s="1"/>
     </row>
@@ -869,10 +874,10 @@
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
       <c r="D23" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>6</v>
@@ -892,19 +897,19 @@
         <v>1</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H24" s="1"/>
     </row>
     <row r="25" ht="36.0" customHeight="1">
       <c r="C25" s="1"/>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="8" t="s">
         <v>44</v>
       </c>
       <c r="F25" s="2" t="s">
@@ -934,13 +939,13 @@
     <row r="27" ht="36.0" customHeight="1">
       <c r="C27" s="1"/>
       <c r="D27" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>8</v>
@@ -954,20 +959,20 @@
       <c r="E28" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F28" s="1" t="s">
-        <v>23</v>
+      <c r="F28" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="29" ht="36.0" customHeight="1">
       <c r="C29" s="1"/>
       <c r="D29" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>4</v>
@@ -979,10 +984,10 @@
     <row r="30" ht="36.0" customHeight="1">
       <c r="C30" s="1"/>
       <c r="D30" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>11</v>
@@ -993,11 +998,11 @@
     </row>
     <row r="31" ht="36.0" customHeight="1">
       <c r="C31" s="1"/>
-      <c r="D31" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>27</v>
+      <c r="D31" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>4</v>
@@ -1009,16 +1014,16 @@
     <row r="32" ht="36.0" customHeight="1">
       <c r="C32" s="1"/>
       <c r="D32" s="1" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H32" s="1"/>
     </row>
@@ -1030,11 +1035,11 @@
       <c r="E33" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F33" s="5" t="s">
-        <v>7</v>
+      <c r="F33" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" ht="36.0" customHeight="1">
@@ -1055,10 +1060,10 @@
     <row r="35" ht="36.0" customHeight="1">
       <c r="C35" s="1"/>
       <c r="D35" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>11</v>
@@ -1069,24 +1074,24 @@
     </row>
     <row r="36" ht="36.0" customHeight="1">
       <c r="C36" s="1"/>
-      <c r="D36" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E36" s="5" t="s">
+      <c r="D36" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E36" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F36" s="3" t="s">
-        <v>34</v>
+      <c r="F36" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H36" s="1"/>
     </row>
     <row r="37" ht="36.0" customHeight="1">
       <c r="C37" s="1"/>
       <c r="D37" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>16</v>
@@ -1100,14 +1105,14 @@
     </row>
     <row r="38" ht="36.0" customHeight="1">
       <c r="C38" s="1"/>
-      <c r="D38" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E38" s="5" t="s">
+      <c r="D38" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>25</v>
+      <c r="E38" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>8</v>
@@ -1134,13 +1139,13 @@
         <v>37</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" ht="36.0" customHeight="1">
@@ -1181,11 +1186,11 @@
       <c r="E43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F43" s="5" t="s">
-        <v>7</v>
+      <c r="F43" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" ht="36.0" customHeight="1">
@@ -1197,7 +1202,7 @@
         <v>10</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>3</v>
@@ -1211,11 +1216,11 @@
       <c r="E45" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F45" s="3" t="s">
-        <v>34</v>
+      <c r="F45" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H45" s="1"/>
     </row>
@@ -1237,10 +1242,10 @@
     <row r="47" ht="36.0" customHeight="1">
       <c r="C47" s="1"/>
       <c r="D47" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>6</v>
@@ -1251,26 +1256,26 @@
     </row>
     <row r="48" ht="36.0" customHeight="1">
       <c r="C48" s="1"/>
-      <c r="D48" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E48" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>23</v>
+      <c r="D48" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E48" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" ht="36.0" customHeight="1">
       <c r="C49" s="1"/>
       <c r="D49" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>11</v>
@@ -1282,25 +1287,25 @@
     <row r="50" ht="36.0" customHeight="1">
       <c r="C50" s="1"/>
       <c r="D50" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51" ht="36.0" customHeight="1">
       <c r="C51" s="1"/>
-      <c r="D51" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>27</v>
+      <c r="D51" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E51" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F51" s="2" t="s">
         <v>6</v>
@@ -1327,26 +1332,26 @@
     <row r="53" ht="36.0" customHeight="1">
       <c r="C53" s="1"/>
       <c r="D53" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H53" s="1"/>
     </row>
     <row r="54" ht="36.0" customHeight="1">
       <c r="C54" s="1"/>
       <c r="D54" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>2</v>
@@ -1373,10 +1378,10 @@
     <row r="56" ht="36.0" customHeight="1">
       <c r="C56" s="1"/>
       <c r="D56" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F56" s="2" t="s">
         <v>6</v>
@@ -1391,7 +1396,7 @@
         <v>37</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F57" s="2" t="s">
         <v>11</v>
@@ -1402,26 +1407,26 @@
     </row>
     <row r="58" ht="36.0" customHeight="1">
       <c r="C58" s="1"/>
-      <c r="D58" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E58" s="5" t="s">
+      <c r="D58" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="F58" s="1" t="s">
-        <v>23</v>
+      <c r="E58" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" ht="36.0" customHeight="1">
       <c r="C59" s="1"/>
-      <c r="D59" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>27</v>
+      <c r="D59" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>6</v>
@@ -1438,26 +1443,26 @@
       <c r="E60" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F60" s="5" t="s">
-        <v>7</v>
+      <c r="F60" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61" ht="36.0" customHeight="1">
       <c r="C61" s="1"/>
-      <c r="D61" s="5" t="s">
+      <c r="D61" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E61" s="5" t="s">
+      <c r="E61" s="8" t="s">
         <v>40</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="62" ht="36.0" customHeight="1">
@@ -1478,16 +1483,16 @@
     <row r="63" ht="36.0" customHeight="1">
       <c r="C63" s="1"/>
       <c r="D63" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F63" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="F63" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="G63" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H63" s="1"/>
     </row>
@@ -1508,17 +1513,17 @@
     </row>
     <row r="65" ht="36.0" customHeight="1">
       <c r="C65" s="1"/>
-      <c r="D65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F65" s="1" t="s">
+      <c r="D65" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E65" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G65" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H65" s="1"/>
     </row>
@@ -1540,16 +1545,16 @@
     <row r="67" ht="36.0" customHeight="1">
       <c r="C67" s="1"/>
       <c r="D67" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68" ht="36.0" customHeight="1">
@@ -1569,42 +1574,42 @@
     </row>
     <row r="69" ht="36.0" customHeight="1">
       <c r="C69" s="1"/>
-      <c r="D69" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F69" s="1" t="s">
+      <c r="D69" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E69" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G69" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H69" s="1"/>
     </row>
     <row r="70" ht="36.0" customHeight="1">
       <c r="C70" s="1"/>
       <c r="D70" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="71" ht="36.0" customHeight="1">
       <c r="C71" s="1"/>
-      <c r="D71" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>27</v>
+      <c r="D71" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E71" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>11</v>
@@ -1616,16 +1621,16 @@
     <row r="72" ht="36.0" customHeight="1">
       <c r="C72" s="1"/>
       <c r="D72" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>34</v>
+        <v>57</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H72" s="1"/>
     </row>
@@ -1676,10 +1681,10 @@
     </row>
     <row r="76" ht="36.0" customHeight="1">
       <c r="C76" s="1"/>
-      <c r="D76" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E76" s="5" t="s">
+      <c r="D76" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E76" s="8" t="s">
         <v>44</v>
       </c>
       <c r="F76" s="2" t="s">
@@ -1692,7 +1697,7 @@
     <row r="77" ht="36.0" customHeight="1">
       <c r="C77" s="1"/>
       <c r="D77" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>16</v>
@@ -1706,11 +1711,11 @@
     </row>
     <row r="78" ht="36.0" customHeight="1">
       <c r="C78" s="1"/>
-      <c r="D78" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E78" s="5" t="s">
+      <c r="D78" s="8" t="s">
         <v>50</v>
+      </c>
+      <c r="E78" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>11</v>
@@ -1736,17 +1741,17 @@
     </row>
     <row r="80" ht="36.0" customHeight="1">
       <c r="C80" s="1"/>
-      <c r="D80" s="1" t="s">
+      <c r="D80" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F80" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="G80" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="F80" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G80" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="81" ht="36.0" customHeight="1">
@@ -1758,7 +1763,7 @@
         <v>1</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>3</v>
@@ -1772,11 +1777,11 @@
       <c r="E82" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F82" s="3" t="s">
-        <v>34</v>
+      <c r="F82" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G82" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H82" s="1"/>
     </row>
@@ -1818,11 +1823,11 @@
       <c r="E85" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F85" s="1" t="s">
-        <v>23</v>
+      <c r="F85" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="G85" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="86" ht="36.0" customHeight="1">
@@ -1843,41 +1848,41 @@
     <row r="87" ht="36.0" customHeight="1">
       <c r="C87" s="1"/>
       <c r="D87" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F87" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="G87" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88" ht="36.0" customHeight="1">
       <c r="C88" s="1"/>
-      <c r="D88" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E88" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F88" s="1" t="s">
+      <c r="D88" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E88" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G88" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H88" s="1"/>
     </row>
     <row r="89" ht="36.0" customHeight="1">
       <c r="C89" s="1"/>
       <c r="D89" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F89" s="2" t="s">
         <v>14</v>
@@ -1889,26 +1894,26 @@
     <row r="90" ht="36.0" customHeight="1">
       <c r="C90" s="1"/>
       <c r="D90" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F90" s="3" t="s">
-        <v>34</v>
+        <v>23</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G90" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H90" s="1"/>
     </row>
     <row r="91" ht="36.0" customHeight="1">
       <c r="C91" s="1"/>
-      <c r="D91" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E91" s="1" t="s">
-        <v>27</v>
+      <c r="D91" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F91" s="2" t="s">
         <v>2</v>
@@ -1935,10 +1940,10 @@
     <row r="93" ht="36.0" customHeight="1">
       <c r="C93" s="1"/>
       <c r="D93" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>6</v>
@@ -1950,10 +1955,10 @@
     <row r="94" ht="36.0" customHeight="1">
       <c r="C94" s="1"/>
       <c r="D94" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>11</v>
@@ -1970,20 +1975,20 @@
       <c r="E95" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F95" s="1" t="s">
-        <v>23</v>
+      <c r="F95" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="G95" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="96" ht="36.0" customHeight="1">
       <c r="C96" s="1"/>
       <c r="D96" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>6</v>
@@ -1998,37 +2003,37 @@
         <v>37</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>7</v>
+        <v>34</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="G97" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="98" ht="36.0" customHeight="1">
       <c r="C98" s="1"/>
-      <c r="D98" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E98" s="5" t="s">
+      <c r="D98" s="8" t="s">
         <v>52</v>
       </c>
+      <c r="E98" s="8" t="s">
+        <v>53</v>
+      </c>
       <c r="F98" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="99" ht="36.0" customHeight="1">
       <c r="C99" s="1"/>
-      <c r="D99" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E99" s="1" t="s">
-        <v>27</v>
+      <c r="D99" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E99" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>11</v>
@@ -2045,20 +2050,20 @@
       <c r="E100" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>34</v>
+      <c r="F100" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G100" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H100" s="1"/>
     </row>
     <row r="101" ht="36.0" customHeight="1">
       <c r="C101" s="1"/>
-      <c r="D101" s="5" t="s">
+      <c r="D101" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E101" s="5" t="s">
+      <c r="E101" s="8" t="s">
         <v>40</v>
       </c>
       <c r="F101" s="2" t="s">
@@ -2070,27 +2075,27 @@
     </row>
     <row r="102" ht="36.0" customHeight="1">
       <c r="C102" s="1"/>
-      <c r="D102" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E102" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F102" s="1" t="s">
+      <c r="D102" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E102" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F102" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G102" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H102" s="1"/>
     </row>
     <row r="103" ht="36.0" customHeight="1">
       <c r="C103" s="1"/>
       <c r="D103" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F103" s="2" t="s">
         <v>4</v>
@@ -2107,8 +2112,8 @@
       <c r="E104" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F104" s="1" t="s">
-        <v>25</v>
+      <c r="F104" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="G104" s="1" t="s">
         <v>8</v>
@@ -2116,10 +2121,10 @@
     </row>
     <row r="105" ht="36.0" customHeight="1">
       <c r="C105" s="1"/>
-      <c r="D105" s="5" t="s">
+      <c r="D105" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E105" s="5" t="s">
+      <c r="E105" s="8" t="s">
         <v>44</v>
       </c>
       <c r="F105" s="2" t="s">
@@ -2137,27 +2142,27 @@
       <c r="E106" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F106" s="3" t="s">
-        <v>34</v>
+      <c r="F106" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G106" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H106" s="1"/>
     </row>
     <row r="107" ht="36.0" customHeight="1">
       <c r="C107" s="1"/>
-      <c r="D107" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E107" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F107" s="1" t="s">
+      <c r="D107" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E107" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G107" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H107" s="1"/>
     </row>
@@ -2169,20 +2174,20 @@
       <c r="E108" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F108" s="1" t="s">
-        <v>23</v>
+      <c r="F108" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="G108" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="109" ht="36.0" customHeight="1">
       <c r="C109" s="1"/>
       <c r="D109" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F109" s="2" t="s">
         <v>11</v>
@@ -2194,10 +2199,10 @@
     <row r="110" ht="36.0" customHeight="1">
       <c r="C110" s="1"/>
       <c r="D110" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>6</v>
@@ -2208,11 +2213,11 @@
     </row>
     <row r="111" ht="36.0" customHeight="1">
       <c r="C111" s="1"/>
-      <c r="D111" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>27</v>
+      <c r="D111" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>4</v>
@@ -2224,16 +2229,16 @@
     <row r="112" ht="36.0" customHeight="1">
       <c r="C112" s="1"/>
       <c r="D112" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F112" s="5" t="s">
-        <v>7</v>
+        <v>57</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="113" ht="36.0" customHeight="1">
@@ -2269,10 +2274,10 @@
     <row r="115" ht="36.0" customHeight="1">
       <c r="C115" s="1"/>
       <c r="D115" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>11</v>
@@ -2283,24 +2288,24 @@
     </row>
     <row r="116" ht="36.0" customHeight="1">
       <c r="C116" s="1"/>
-      <c r="D116" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E116" s="5" t="s">
+      <c r="D116" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E116" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F116" s="3" t="s">
-        <v>34</v>
+      <c r="F116" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G116" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H116" s="1"/>
     </row>
     <row r="117" ht="36.0" customHeight="1">
       <c r="C117" s="1"/>
       <c r="D117" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E117" s="4" t="s">
         <v>16</v>
@@ -2314,14 +2319,14 @@
     </row>
     <row r="118" ht="36.0" customHeight="1">
       <c r="C118" s="1"/>
-      <c r="D118" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E118" s="5" t="s">
+      <c r="D118" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F118" s="1" t="s">
-        <v>25</v>
+      <c r="E118" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="G118" s="1" t="s">
         <v>8</v>
@@ -2348,7 +2353,7 @@
         <v>37</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>11</v>
@@ -2380,11 +2385,11 @@
       <c r="E122" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F122" s="1" t="s">
-        <v>23</v>
+      <c r="F122" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="G122" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="123" ht="36.0" customHeight="1">
@@ -2410,26 +2415,26 @@
       <c r="E124" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F124" s="5" t="s">
-        <v>7</v>
+      <c r="F124" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="G124" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="125" ht="36.0" customHeight="1">
       <c r="C125" s="1"/>
-      <c r="D125" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E125" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F125" s="1" t="s">
+      <c r="D125" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E125" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F125" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G125" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H125" s="1"/>
     </row>
@@ -2451,26 +2456,26 @@
     <row r="127" ht="36.0" customHeight="1">
       <c r="C127" s="1"/>
       <c r="D127" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E127" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F127" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G127" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E127" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F127" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="H127" s="1"/>
     </row>
     <row r="128" ht="36.0" customHeight="1">
       <c r="C128" s="1"/>
       <c r="D128" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F128" s="2" t="s">
         <v>2</v>
@@ -2482,10 +2487,10 @@
     <row r="129" ht="36.0" customHeight="1">
       <c r="C129" s="1"/>
       <c r="D129" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F129" s="2" t="s">
         <v>11</v>
@@ -2497,10 +2502,10 @@
     <row r="130" ht="36.0" customHeight="1">
       <c r="C130" s="1"/>
       <c r="D130" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>6</v>
@@ -2511,17 +2516,17 @@
     </row>
     <row r="131" ht="36.0" customHeight="1">
       <c r="C131" s="1"/>
-      <c r="D131" s="1" t="s">
+      <c r="D131" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E131" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F131" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E131" s="1" t="s">
+      <c r="G131" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="F131" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G131" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="132" ht="36.0" customHeight="1">
@@ -2542,10 +2547,10 @@
     <row r="133" ht="36.0" customHeight="1">
       <c r="C133" s="1"/>
       <c r="D133" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F133" s="2" t="s">
         <v>6</v>
@@ -2557,16 +2562,16 @@
     <row r="134" ht="36.0" customHeight="1">
       <c r="C134" s="1"/>
       <c r="D134" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F134" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G134" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H134" s="1"/>
     </row>
@@ -2578,20 +2583,20 @@
       <c r="E135" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F135" s="1" t="s">
-        <v>23</v>
+      <c r="F135" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="G135" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="136" ht="36.0" customHeight="1">
       <c r="C136" s="1"/>
       <c r="D136" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>11</v>
@@ -2606,7 +2611,7 @@
         <v>37</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>4</v>
@@ -2617,32 +2622,32 @@
     </row>
     <row r="138" ht="36.0" customHeight="1">
       <c r="C138" s="1"/>
-      <c r="D138" s="1" t="s">
+      <c r="D138" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E138" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F138" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E138" s="1" t="s">
+      <c r="G138" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="F138" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="139" ht="36.0" customHeight="1">
       <c r="C139" s="1"/>
-      <c r="D139" s="8" t="s">
-        <v>42</v>
+      <c r="D139" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F139" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
+      </c>
+      <c r="F139" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="G139" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H139" s="1"/>
     </row>
@@ -2663,17 +2668,17 @@
     </row>
     <row r="141" ht="36.0" customHeight="1">
       <c r="C141" s="1"/>
-      <c r="D141" s="5" t="s">
+      <c r="D141" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E141" s="5" t="s">
+      <c r="E141" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F141" s="3" t="s">
-        <v>34</v>
+      <c r="F141" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G141" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H141" s="1"/>
     </row>
@@ -2695,16 +2700,16 @@
     <row r="143" ht="36.0" customHeight="1">
       <c r="C143" s="1"/>
       <c r="D143" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
+      </c>
+      <c r="F143" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="G143" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="144" ht="36.0" customHeight="1">
@@ -2724,10 +2729,10 @@
     </row>
     <row r="145" ht="36.0" customHeight="1">
       <c r="C145" s="1"/>
-      <c r="D145" s="5" t="s">
+      <c r="D145" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E145" s="5" t="s">
+      <c r="E145" s="8" t="s">
         <v>44</v>
       </c>
       <c r="F145" s="2" t="s">
@@ -2755,16 +2760,16 @@
     <row r="147" ht="36.0" customHeight="1">
       <c r="C147" s="1"/>
       <c r="D147" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F147" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G147" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H147" s="1"/>
     </row>
@@ -2786,10 +2791,10 @@
     <row r="149" ht="36.0" customHeight="1">
       <c r="C149" s="1"/>
       <c r="D149" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>2</v>
@@ -2801,10 +2806,10 @@
     <row r="150" ht="36.0" customHeight="1">
       <c r="C150" s="1"/>
       <c r="D150" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F150" s="2" t="s">
         <v>6</v>
@@ -2815,14 +2820,14 @@
     </row>
     <row r="151" ht="36.0" customHeight="1">
       <c r="C151" s="1"/>
-      <c r="D151" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>25</v>
+      <c r="D151" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E151" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F151" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="G151" s="1" t="s">
         <v>8</v>
@@ -2831,16 +2836,16 @@
     <row r="152" ht="36.0" customHeight="1">
       <c r="C152" s="1"/>
       <c r="D152" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F152" s="3" t="s">
-        <v>34</v>
+        <v>57</v>
+      </c>
+      <c r="F152" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G152" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H152" s="1"/>
     </row>
@@ -2877,13 +2882,13 @@
     <row r="155" ht="36.0" customHeight="1">
       <c r="C155" s="1"/>
       <c r="D155" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="F155" s="2" t="s">
         <v>21</v>
-      </c>
-      <c r="E155" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F155" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="G155" s="2" t="s">
         <v>3</v>
@@ -2891,23 +2896,23 @@
     </row>
     <row r="156" ht="36.0" customHeight="1">
       <c r="C156" s="1"/>
-      <c r="D156" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E156" s="5" t="s">
+      <c r="D156" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E156" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F156" s="1" t="s">
-        <v>23</v>
+      <c r="F156" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="G156" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="157" ht="36.0" customHeight="1">
       <c r="C157" s="1"/>
       <c r="D157" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E157" s="4" t="s">
         <v>16</v>
@@ -2921,32 +2926,32 @@
     </row>
     <row r="158" ht="36.0" customHeight="1">
       <c r="C158" s="1"/>
-      <c r="D158" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E158" s="5" t="s">
+      <c r="D158" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F158" s="5" t="s">
-        <v>7</v>
+      <c r="E158" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F158" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="G158" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="159" ht="36.0" customHeight="1">
       <c r="C159" s="1"/>
-      <c r="D159" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F159" s="1" t="s">
+      <c r="D159" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E159" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F159" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G159" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H159" s="1"/>
     </row>
@@ -2956,7 +2961,7 @@
         <v>37</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F160" s="2" t="s">
         <v>11</v>
@@ -2973,11 +2978,11 @@
       <c r="E161" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F161" s="3" t="s">
-        <v>34</v>
+      <c r="F161" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G161" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H161" s="1"/>
     </row>
@@ -3013,17 +3018,17 @@
     </row>
     <row r="164" ht="36.0" customHeight="1">
       <c r="C164" s="1"/>
-      <c r="D164" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E164" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F164" s="1" t="s">
+      <c r="D164" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E164" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F164" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G164" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H164" s="1"/>
     </row>
@@ -3060,10 +3065,10 @@
     <row r="167" ht="36.0" customHeight="1">
       <c r="C167" s="1"/>
       <c r="D167" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F167" s="2" t="s">
         <v>6</v>
@@ -3075,25 +3080,25 @@
     <row r="168" ht="36.0" customHeight="1">
       <c r="C168" s="1"/>
       <c r="D168" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F168" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="F168" s="5" t="s">
+        <v>24</v>
+      </c>
       <c r="G168" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="169" ht="36.0" customHeight="1">
       <c r="C169" s="1"/>
       <c r="D169" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F169" s="2" t="s">
         <v>15</v>
@@ -3105,10 +3110,10 @@
     <row r="170" ht="36.0" customHeight="1">
       <c r="C170" s="1"/>
       <c r="D170" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F170" s="2" t="s">
         <v>6</v>
@@ -3119,11 +3124,11 @@
     </row>
     <row r="171" ht="36.0" customHeight="1">
       <c r="C171" s="1"/>
-      <c r="D171" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E171" s="1" t="s">
-        <v>27</v>
+      <c r="D171" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E171" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F171" s="2" t="s">
         <v>6</v>
@@ -3141,20 +3146,20 @@
         <v>13</v>
       </c>
       <c r="F172" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G172" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H172" s="1"/>
     </row>
     <row r="173" ht="36.0" customHeight="1">
       <c r="C173" s="1"/>
       <c r="D173" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F173" s="2" t="s">
         <v>11</v>
@@ -3166,10 +3171,10 @@
     <row r="174" ht="36.0" customHeight="1">
       <c r="C174" s="1"/>
       <c r="D174" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F174" s="2" t="s">
         <v>4</v>
@@ -3186,26 +3191,26 @@
       <c r="E175" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F175" s="5" t="s">
-        <v>7</v>
+      <c r="F175" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="G175" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="176" ht="36.0" customHeight="1">
       <c r="C176" s="1"/>
-      <c r="D176" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E176" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F176" s="1" t="s">
+      <c r="D176" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E176" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G176" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H176" s="1"/>
     </row>
@@ -3215,7 +3220,7 @@
         <v>37</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F177" s="2" t="s">
         <v>4</v>
@@ -3226,11 +3231,11 @@
     </row>
     <row r="178" ht="36.0" customHeight="1">
       <c r="C178" s="1"/>
-      <c r="D178" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E178" s="5" t="s">
+      <c r="D178" s="8" t="s">
         <v>52</v>
+      </c>
+      <c r="E178" s="8" t="s">
+        <v>53</v>
       </c>
       <c r="F178" s="2" t="s">
         <v>11</v>
@@ -3241,11 +3246,11 @@
     </row>
     <row r="179" ht="36.0" customHeight="1">
       <c r="C179" s="1"/>
-      <c r="D179" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E179" s="1" t="s">
-        <v>27</v>
+      <c r="D179" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E179" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F179" s="2" t="s">
         <v>6</v>
@@ -3262,27 +3267,27 @@
       <c r="E180" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F180" s="3" t="s">
-        <v>34</v>
+      <c r="F180" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G180" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H180" s="1"/>
     </row>
     <row r="181" ht="36.0" customHeight="1">
       <c r="C181" s="1"/>
-      <c r="D181" s="5" t="s">
+      <c r="D181" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E181" s="5" t="s">
+      <c r="E181" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F181" s="1" t="s">
-        <v>23</v>
+      <c r="F181" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="G181" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="182" ht="36.0" customHeight="1">
@@ -3302,17 +3307,17 @@
     </row>
     <row r="183" ht="36.0" customHeight="1">
       <c r="C183" s="1"/>
-      <c r="D183" s="1" t="s">
+      <c r="D183" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E183" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F183" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E183" s="1" t="s">
+      <c r="G183" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="F183" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G183" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="184" ht="36.0" customHeight="1">
@@ -3332,10 +3337,10 @@
     </row>
     <row r="185" ht="36.0" customHeight="1">
       <c r="C185" s="1"/>
-      <c r="D185" s="5" t="s">
+      <c r="D185" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E185" s="5" t="s">
+      <c r="E185" s="8" t="s">
         <v>44</v>
       </c>
       <c r="F185" s="2" t="s">
@@ -3363,16 +3368,16 @@
     <row r="187" ht="36.0" customHeight="1">
       <c r="C187" s="1"/>
       <c r="D187" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F187" s="3" t="s">
-        <v>34</v>
+        <v>23</v>
+      </c>
+      <c r="F187" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G187" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H187" s="1"/>
     </row>
@@ -3394,10 +3399,10 @@
     <row r="189" ht="36.0" customHeight="1">
       <c r="C189" s="1"/>
       <c r="D189" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F189" s="2" t="s">
         <v>11</v>
@@ -3414,20 +3419,20 @@
       <c r="E190" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F190" s="5" t="s">
-        <v>7</v>
+      <c r="F190" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="G190" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="191" ht="36.0" customHeight="1">
       <c r="C191" s="1"/>
-      <c r="D191" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E191" s="1" t="s">
-        <v>27</v>
+      <c r="D191" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E191" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F191" s="2" t="s">
         <v>6</v>
@@ -3439,16 +3444,16 @@
     <row r="192" ht="36.0" customHeight="1">
       <c r="C192" s="1"/>
       <c r="D192" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F192" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G192" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H192" s="1"/>
     </row>
@@ -3485,13 +3490,13 @@
     <row r="195" ht="36.0" customHeight="1">
       <c r="C195" s="1"/>
       <c r="D195" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F195" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="F195" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="G195" s="1" t="s">
         <v>8</v>
@@ -3499,24 +3504,24 @@
     </row>
     <row r="196" ht="36.0" customHeight="1">
       <c r="C196" s="1"/>
-      <c r="D196" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E196" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F196" s="1" t="s">
+      <c r="D196" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E196" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F196" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G196" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H196" s="1"/>
     </row>
     <row r="197" ht="36.0" customHeight="1">
       <c r="C197" s="1"/>
       <c r="D197" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E197" s="4" t="s">
         <v>16</v>
@@ -3530,11 +3535,11 @@
     </row>
     <row r="198" ht="36.0" customHeight="1">
       <c r="C198" s="1"/>
-      <c r="D198" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E198" s="5" t="s">
+      <c r="D198" s="8" t="s">
         <v>50</v>
+      </c>
+      <c r="E198" s="8" t="s">
+        <v>51</v>
       </c>
       <c r="F198" s="2" t="s">
         <v>6</v>
@@ -3545,17 +3550,17 @@
     </row>
     <row r="199" ht="36.0" customHeight="1">
       <c r="C199" s="1"/>
-      <c r="D199" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E199" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F199" s="1" t="s">
+      <c r="D199" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E199" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F199" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G199" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H199" s="1"/>
     </row>
@@ -3565,7 +3570,7 @@
         <v>37</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F200" s="2" t="s">
         <v>14</v>
@@ -3582,11 +3587,11 @@
       <c r="E201" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F201" s="5" t="s">
-        <v>7</v>
+      <c r="F201" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="G201" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="202" ht="36.0" customHeight="1">
@@ -3627,11 +3632,11 @@
       <c r="E204" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F204" s="3" t="s">
-        <v>34</v>
+      <c r="F204" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G204" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H204" s="1"/>
     </row>
@@ -3643,11 +3648,11 @@
       <c r="E205" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F205" s="1" t="s">
-        <v>23</v>
+      <c r="F205" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="G205" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="206" ht="36.0" customHeight="1">
@@ -3668,10 +3673,10 @@
     <row r="207" ht="36.0" customHeight="1">
       <c r="C207" s="1"/>
       <c r="D207" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F207" s="2" t="s">
         <v>6</v>
@@ -3683,40 +3688,40 @@
     <row r="208" ht="36.0" customHeight="1">
       <c r="C208" s="1"/>
       <c r="D208" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F208" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
+      </c>
+      <c r="F208" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="G208" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="209" ht="36.0" customHeight="1">
       <c r="C209" s="1"/>
       <c r="D209" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="210" ht="36.0" customHeight="1">
       <c r="C210" s="1"/>
       <c r="D210" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F210" s="2" t="s">
         <v>11</v>
@@ -3727,11 +3732,11 @@
     </row>
     <row r="211" ht="36.0" customHeight="1">
       <c r="C211" s="1"/>
-      <c r="D211" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E211" s="1" t="s">
-        <v>27</v>
+      <c r="D211" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E211" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F211" s="2" t="s">
         <v>4</v>
@@ -3748,37 +3753,37 @@
       <c r="E212" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F212" s="3" t="s">
-        <v>34</v>
+      <c r="F212" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G212" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H212" s="1"/>
     </row>
     <row r="213" ht="36.0" customHeight="1">
       <c r="C213" s="1"/>
-      <c r="D213" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E213" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F213" s="1" t="s">
+      <c r="D213" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E213" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F213" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G213" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H213" s="1"/>
     </row>
     <row r="214" ht="36.0" customHeight="1">
       <c r="C214" s="1"/>
       <c r="D214" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E214" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F214" s="2" t="s">
         <v>4</v>
@@ -3795,20 +3800,20 @@
       <c r="E215" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F215" s="5" t="s">
-        <v>7</v>
+      <c r="F215" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="G215" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="216" ht="36.0" customHeight="1">
       <c r="C216" s="1"/>
       <c r="D216" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F216" s="2" t="s">
         <v>6</v>
@@ -3819,43 +3824,43 @@
     </row>
     <row r="217" ht="36.0" customHeight="1">
       <c r="C217" s="1"/>
-      <c r="D217" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E217" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F217" s="1" t="s">
+      <c r="D217" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E217" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F217" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G217" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H217" s="1"/>
     </row>
     <row r="218" ht="36.0" customHeight="1">
       <c r="C218" s="1"/>
-      <c r="D218" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="E218" s="5" t="s">
+      <c r="D218" s="8" t="s">
         <v>52</v>
       </c>
+      <c r="E218" s="8" t="s">
+        <v>53</v>
+      </c>
       <c r="F218" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H218" s="1"/>
     </row>
     <row r="219" ht="36.0" customHeight="1">
       <c r="C219" s="1"/>
-      <c r="D219" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E219" s="1" t="s">
-        <v>27</v>
+      <c r="D219" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E219" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>11</v>
@@ -3881,14 +3886,14 @@
     </row>
     <row r="221" ht="36.0" customHeight="1">
       <c r="C221" s="1"/>
-      <c r="D221" s="5" t="s">
+      <c r="D221" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E221" s="5" t="s">
+      <c r="E221" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F221" s="1" t="s">
-        <v>25</v>
+      <c r="F221" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="G221" s="1" t="s">
         <v>8</v>
@@ -3902,20 +3907,20 @@
       <c r="E222" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F222" s="1" t="s">
-        <v>23</v>
+      <c r="F222" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="G222" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="223" ht="36.0" customHeight="1">
       <c r="C223" s="1"/>
       <c r="D223" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E223" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F223" s="2" t="s">
         <v>2</v>
@@ -3941,17 +3946,17 @@
     </row>
     <row r="225" ht="36.0" customHeight="1">
       <c r="C225" s="1"/>
-      <c r="D225" s="5" t="s">
+      <c r="D225" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E225" s="5" t="s">
+      <c r="E225" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F225" s="5" t="s">
-        <v>7</v>
+      <c r="F225" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="G225" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="226" ht="36.0" customHeight="1">
@@ -3972,10 +3977,10 @@
     <row r="227" ht="36.0" customHeight="1">
       <c r="C227" s="1"/>
       <c r="D227" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F227" s="2" t="s">
         <v>14</v>
@@ -3993,23 +3998,23 @@
         <v>5</v>
       </c>
       <c r="F228" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G228" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H228" s="1"/>
     </row>
     <row r="229" ht="36.0" customHeight="1">
       <c r="C229" s="1"/>
       <c r="D229" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G229" s="2" t="s">
         <v>3</v>
@@ -4018,10 +4023,10 @@
     <row r="230" ht="36.0" customHeight="1">
       <c r="C230" s="1"/>
       <c r="D230" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F230" s="2" t="s">
         <v>2</v>
@@ -4032,11 +4037,11 @@
     </row>
     <row r="231" ht="36.0" customHeight="1">
       <c r="C231" s="1"/>
-      <c r="D231" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E231" s="1" t="s">
-        <v>27</v>
+      <c r="D231" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E231" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F231" s="2" t="s">
         <v>11</v>
@@ -4053,26 +4058,26 @@
       <c r="E232" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F232" s="1" t="s">
-        <v>25</v>
+      <c r="F232" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="233" ht="36.0" customHeight="1">
       <c r="C233" s="1"/>
-      <c r="D233" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E233" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F233" s="1" t="s">
+      <c r="D233" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E233" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F233" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G233" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H233" s="1"/>
     </row>
@@ -4094,10 +4099,10 @@
     <row r="235" ht="36.0" customHeight="1">
       <c r="C235" s="1"/>
       <c r="D235" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F235" s="2" t="s">
         <v>6</v>
@@ -4108,48 +4113,48 @@
     </row>
     <row r="236" ht="36.0" customHeight="1">
       <c r="C236" s="1"/>
-      <c r="D236" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E236" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F236" s="1" t="s">
+      <c r="D236" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E236" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F236" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G236" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H236" s="1"/>
     </row>
     <row r="237" ht="36.0" customHeight="1">
       <c r="C237" s="1"/>
       <c r="D237" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E237" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F237" s="5" t="s">
-        <v>7</v>
+      <c r="F237" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="G237" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="238" ht="36.0" customHeight="1">
       <c r="C238" s="1"/>
-      <c r="D238" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E238" s="5" t="s">
+      <c r="D238" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F238" s="3" t="s">
-        <v>34</v>
+      <c r="E238" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F238" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G238" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H238" s="1"/>
     </row>
@@ -4174,28 +4179,28 @@
         <v>37</v>
       </c>
       <c r="E240" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F240" s="1" t="s">
-        <v>23</v>
+        <v>34</v>
+      </c>
+      <c r="F240" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="G240" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="241" ht="36.0" customHeight="1">
       <c r="C241" s="1"/>
-      <c r="D241" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E241" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F241" s="1" t="s">
+      <c r="D241" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E241" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F241" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G241" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H241" s="1"/>
     </row>
@@ -4237,11 +4242,11 @@
       <c r="E244" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F244" s="5" t="s">
-        <v>7</v>
+      <c r="F244" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="G244" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="245" ht="36.0" customHeight="1">
@@ -4268,35 +4273,35 @@
         <v>16</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="247" ht="36.0" customHeight="1">
       <c r="C247" s="1"/>
       <c r="D247" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E247" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F247" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G247" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E247" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F247" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G247" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="H247" s="1"/>
     </row>
     <row r="248" ht="36.0" customHeight="1">
       <c r="C248" s="1"/>
       <c r="D248" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F248" s="2" t="s">
         <v>4</v>
@@ -4308,10 +4313,10 @@
     <row r="249" ht="36.0" customHeight="1">
       <c r="C249" s="1"/>
       <c r="D249" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F249" s="2" t="s">
         <v>6</v>
@@ -4323,10 +4328,10 @@
     <row r="250" ht="36.0" customHeight="1">
       <c r="C250" s="1"/>
       <c r="D250" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F250" s="2" t="s">
         <v>6</v>
@@ -4337,17 +4342,17 @@
     </row>
     <row r="251" ht="36.0" customHeight="1">
       <c r="C251" s="1"/>
-      <c r="D251" s="1" t="s">
+      <c r="D251" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E251" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F251" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E251" s="1" t="s">
+      <c r="G251" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="F251" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G251" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="252" ht="36.0" customHeight="1">
@@ -4368,10 +4373,10 @@
     <row r="253" ht="36.0" customHeight="1">
       <c r="C253" s="1"/>
       <c r="D253" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F253" s="2" t="s">
         <v>6</v>
@@ -4383,42 +4388,42 @@
     <row r="254" ht="36.0" customHeight="1">
       <c r="C254" s="1"/>
       <c r="D254" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E254" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F254" s="3" t="s">
         <v>34</v>
       </c>
+      <c r="F254" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="G254" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H254" s="1"/>
     </row>
     <row r="255" ht="36.0" customHeight="1">
       <c r="C255" s="1"/>
-      <c r="D255" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E255" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F255" s="1" t="s">
+      <c r="D255" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E255" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F255" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G255" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H255" s="1"/>
     </row>
     <row r="256" ht="36.0" customHeight="1">
       <c r="C256" s="1"/>
       <c r="D256" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F256" s="2" t="s">
         <v>11</v>
@@ -4433,13 +4438,13 @@
         <v>37</v>
       </c>
       <c r="E257" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F257" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
+      </c>
+      <c r="F257" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H257" s="1"/>
     </row>
@@ -4451,20 +4456,20 @@
       <c r="E258" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F258" s="5" t="s">
-        <v>7</v>
+      <c r="F258" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="259" ht="36.0" customHeight="1">
       <c r="C259" s="1"/>
-      <c r="D259" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E259" s="1" t="s">
-        <v>27</v>
+      <c r="D259" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E259" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F259" s="2" t="s">
         <v>4</v>
@@ -4481,26 +4486,26 @@
       <c r="E260" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F260" s="1" t="s">
-        <v>23</v>
+      <c r="F260" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="261" ht="36.0" customHeight="1">
       <c r="C261" s="1"/>
-      <c r="D261" s="5" t="s">
+      <c r="D261" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E261" s="5" t="s">
+      <c r="E261" s="8" t="s">
         <v>40</v>
       </c>
       <c r="F261" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H261" s="1"/>
     </row>
@@ -4522,10 +4527,10 @@
     <row r="263" ht="36.0" customHeight="1">
       <c r="C263" s="1"/>
       <c r="D263" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E263" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F263" s="2" t="s">
         <v>11</v>
@@ -4542,19 +4547,19 @@
       <c r="E264" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F264" s="1" t="s">
-        <v>25</v>
+      <c r="F264" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="265" ht="36.0" customHeight="1">
       <c r="C265" s="1"/>
-      <c r="D265" s="5" t="s">
+      <c r="D265" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="E265" s="5" t="s">
+      <c r="E265" s="8" t="s">
         <v>44</v>
       </c>
       <c r="F265" s="2" t="s">
@@ -4573,7 +4578,7 @@
         <v>10</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G266" s="2" t="s">
         <v>3</v>
@@ -4582,16 +4587,16 @@
     <row r="267" ht="36.0" customHeight="1">
       <c r="C267" s="1"/>
       <c r="D267" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F267" s="3" t="s">
-        <v>34</v>
+        <v>23</v>
+      </c>
+      <c r="F267" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H267" s="1"/>
     </row>
@@ -4613,10 +4618,10 @@
     <row r="269" ht="36.0" customHeight="1">
       <c r="C269" s="1"/>
       <c r="D269" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F269" s="2" t="s">
         <v>6</v>
@@ -4628,25 +4633,25 @@
     <row r="270" ht="36.0" customHeight="1">
       <c r="C270" s="1"/>
       <c r="D270" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F270" s="5" t="s">
-        <v>7</v>
+        <v>20</v>
+      </c>
+      <c r="F270" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="271" ht="36.0" customHeight="1">
       <c r="C271" s="1"/>
-      <c r="D271" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E271" s="1" t="s">
-        <v>27</v>
+      <c r="D271" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E271" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F271" s="2" t="s">
         <v>11</v>
@@ -4658,16 +4663,16 @@
     <row r="272" ht="36.0" customHeight="1">
       <c r="C272" s="1"/>
       <c r="D272" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E272" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F272" s="3" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G272" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H272" s="1"/>
     </row>
@@ -4703,39 +4708,39 @@
     </row>
     <row r="275" ht="36.0" customHeight="1">
       <c r="C275" s="1"/>
-      <c r="D275" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E275" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F275" s="1" t="s">
+      <c r="D275" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E275" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F275" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G275" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H275" s="1"/>
     </row>
     <row r="276" ht="36.0" customHeight="1">
       <c r="C276" s="1"/>
-      <c r="D276" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E276" s="5" t="s">
+      <c r="D276" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E276" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="F276" s="1" t="s">
-        <v>25</v>
+      <c r="F276" s="5" t="s">
+        <v>26</v>
       </c>
       <c r="G276" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="277" ht="36.0" customHeight="1">
       <c r="C277" s="1"/>
       <c r="D277" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E277" s="4" t="s">
         <v>16</v>
@@ -4749,17 +4754,17 @@
     </row>
     <row r="278" ht="36.0" customHeight="1">
       <c r="C278" s="1"/>
-      <c r="D278" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E278" s="5" t="s">
+      <c r="D278" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="F278" s="1" t="s">
-        <v>23</v>
+      <c r="E278" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="F278" s="5" t="s">
+        <v>24</v>
       </c>
       <c r="G278" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="279" ht="36.0" customHeight="1">
@@ -4770,11 +4775,11 @@
       <c r="E279" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F279" s="3" t="s">
-        <v>34</v>
+      <c r="F279" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G279" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H279" s="1"/>
     </row>
@@ -4784,7 +4789,7 @@
         <v>37</v>
       </c>
       <c r="E280" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F280" s="2" t="s">
         <v>15</v>
@@ -4816,11 +4821,11 @@
       <c r="E282" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F282" s="5" t="s">
-        <v>7</v>
+      <c r="F282" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="283" ht="36.0" customHeight="1">
@@ -4832,10 +4837,10 @@
         <v>1</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="284" ht="36.0" customHeight="1">
@@ -4855,17 +4860,17 @@
     </row>
     <row r="285" ht="36.0" customHeight="1">
       <c r="C285" s="1"/>
-      <c r="D285" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E285" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F285" s="1" t="s">
+      <c r="D285" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E285" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F285" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G285" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H285" s="1"/>
     </row>
@@ -4887,26 +4892,26 @@
     <row r="287" ht="36.0" customHeight="1">
       <c r="C287" s="1"/>
       <c r="D287" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E287" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F287" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G287" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E287" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F287" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G287" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="H287" s="1"/>
     </row>
     <row r="288" ht="36.0" customHeight="1">
       <c r="C288" s="1"/>
       <c r="D288" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F288" s="2" t="s">
         <v>4</v>
@@ -4918,10 +4923,10 @@
     <row r="289" ht="36.0" customHeight="1">
       <c r="C289" s="1"/>
       <c r="D289" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F289" s="2" t="s">
         <v>11</v>
@@ -4933,10 +4938,10 @@
     <row r="290" ht="36.0" customHeight="1">
       <c r="C290" s="1"/>
       <c r="D290" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F290" s="5" t="s">
         <v>7</v>
@@ -4947,59 +4952,59 @@
     </row>
     <row r="291" ht="36.0" customHeight="1">
       <c r="C291" s="1"/>
-      <c r="D291" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E291" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F291" s="1" t="s">
+      <c r="D291" s="5" t="s">
         <v>28</v>
       </c>
+      <c r="E291" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="F291" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="G291" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H291" s="1"/>
     </row>
     <row r="292" ht="36.0" customHeight="1">
       <c r="C292" s="1"/>
-      <c r="D292" s="8" t="s">
-        <v>42</v>
+      <c r="D292" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F292" s="1" t="s">
-        <v>28</v>
+        <v>36</v>
+      </c>
+      <c r="F292" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="G292" s="1" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="H292" s="1"/>
     </row>
     <row r="293" ht="36.0" customHeight="1">
       <c r="C293" s="1"/>
       <c r="D293" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="F293" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
+      </c>
+      <c r="F293" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="G293" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H293" s="1"/>
     </row>
     <row r="294" ht="36.0" customHeight="1">
       <c r="C294" s="1"/>
       <c r="D294" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E294" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F294" s="2" t="s">
         <v>11</v>
@@ -5016,20 +5021,20 @@
       <c r="E295" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F295" s="1" t="s">
-        <v>23</v>
+      <c r="F295" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="296" ht="36.0" customHeight="1">
       <c r="C296" s="1"/>
       <c r="D296" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F296" s="2" t="s">
         <v>4</v>
@@ -5044,7 +5049,7 @@
         <v>37</v>
       </c>
       <c r="E297" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F297" s="2" t="s">
         <v>11</v>
@@ -5061,20 +5066,20 @@
       <c r="E298" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="F298" s="5" t="s">
-        <v>7</v>
+      <c r="F298" s="8" t="s">
+        <v>26</v>
       </c>
       <c r="G298" s="1" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="299" ht="36.0" customHeight="1">
       <c r="C299" s="1"/>
-      <c r="D299" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E299" s="1" t="s">
-        <v>27</v>
+      <c r="D299" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E299" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="F299" s="2" t="s">
         <v>6</v>
@@ -5166,7 +5171,7 @@
     </row>
     <row r="311" ht="36.0" customHeight="1">
       <c r="C311" s="1"/>
-      <c r="D311" s="8"/>
+      <c r="D311" s="5"/>
       <c r="E311" s="1"/>
       <c r="F311" s="2"/>
       <c r="G311" s="2"/>
